--- a/working_hours.xlsx
+++ b/working_hours.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzk-my.sharepoint.com/personal/linus_palm_uzk_onmicrosoft_com/Documents/Master/MA/master-thesis-nurse-scheduling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{EE25CD3E-51E2-CC4B-802E-B9D2B57E0F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB6885A9-3BBE-2A4B-85FD-C853879E2BD3}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{EE25CD3E-51E2-CC4B-802E-B9D2B57E0F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87006116-5CBC-FE4F-8698-40E2B574EE45}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9420" yWindow="3220" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dienstplan" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Name</t>
   </si>
@@ -102,13 +102,16 @@
   </si>
   <si>
     <t>N18</t>
+  </si>
+  <si>
+    <t>hours/week fulltime</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,6 +132,14 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -186,7 +197,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -200,6 +211,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Prozent" xfId="3" builtinId="5"/>
@@ -218,6 +230,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -505,13 +521,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,206 +538,252 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E1" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <f t="shared" ref="B2:B21" si="0">38.5*C2</f>
-        <v>0</v>
-      </c>
-      <c r="C2" s="7"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C2</f>
+        <v>34.65</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="E2" s="6">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C3" s="4"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C3</f>
+        <v>38.5</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C4</f>
+        <v>38.5</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C5</f>
+        <v>38.5</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C6</f>
+        <v>38.5</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C7</f>
+        <v>38.5</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C8</f>
+        <v>38.5</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C9</f>
+        <v>38.5</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C10" s="4"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C10</f>
+        <v>38.5</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C11</f>
+        <v>38.5</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C12</f>
+        <v>38.5</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C13</f>
+        <v>34.65</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C14</f>
+        <v>34.65</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <f>E2*C15</f>
+        <v>34.65</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C16" s="4"/>
+        <f>E2*C16</f>
+        <v>30.8</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C17" s="4"/>
+        <f>E2*C17</f>
+        <v>26.95</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C18" s="4"/>
+        <f>E2*C18</f>
+        <v>21.175000000000001</v>
+      </c>
+      <c r="C18" s="4">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B19" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C19" s="4"/>
+        <f>E2*C19</f>
+        <v>21.175000000000001</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>21</v>
       </c>
       <c r="B20" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C20" s="4"/>
+        <f>E2*C20</f>
+        <v>11.549999999999999</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C21" s="5"/>
+        <f>E2*C21</f>
+        <v>11.549999999999999</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0.3</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
